--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_09-07-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_09-07-2025.xlsx
@@ -802,7 +802,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/celotex-ga4060-2400x1200x60mm (Caused by SSLError(SSLEOFError(8, '[SSL: UNEXPECTED_EOF_WHILE_READING] EOF occurred in violation of protocol (_ssl.c:1006)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>£43.50</t>
+          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/150mm-celotex-xr4150-2-4m-x-1-2m (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x000001F592225990&gt;, 'Connection to build4less.co.uk timed out. (connect timeout=None)'))</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2344,7 +2344,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>£79.12</t>
+          <t>Error: 522 Server Error:  for url: https://www.planetinsulation.co.uk/products/celotex-pl4000-insulation-boards?variant=42844828827885</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2364,7 +2364,7 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>£45.67</t>
+          <t>Error: 522 Server Error:  for url: https://diybuildingsupplies.co.uk/products/celotex-pl4040-high-performance-board-insulation-2400-x-1200-x-52-5mm</t>
         </is>
       </c>
     </row>
@@ -2461,7 +2461,7 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>£50.69</t>
+          <t>Error: 522 Server Error:  for url: https://diybuildingsupplies.co.uk/products/62-5mm-celotex-pl4050-pir-insulated-plasterboard-2400mm-x-1200mm</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>£55.30</t>
+          <t>Error: 522 Server Error:  for url: https://diybuildingsupplies.co.uk/products/celotex-pl4060-high-performance-board-insulation-2400-x-1200-x-72-5mm</t>
         </is>
       </c>
     </row>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>£44.60</t>
+          <t>Error: 522 Server Error:  for url: https://build4less.co.uk/products/celotex-cavitywall-47mm</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>£61.00</t>
+          <t>Error: 'NoneType' object has no attribute 'find'</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2752,7 +2752,7 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>£49.06</t>
+          <t>Error: 522 Server Error:  for url: https://diybuildingsupplies.co.uk/products/75mm-celotex-cw4075-cavity-insulation-1200mm-x-450mm-8-boards</t>
         </is>
       </c>
     </row>
@@ -3177,7 +3177,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>POA or Product 'out of stock'</t>
+          <t>Error: 503 Server Error: Service Unavailable for url: https://materialsmarket.com/products/140mm-celotex-thermaclass-cavity-wall-21-full-fill-insulation-board-t-g-1190mm-x-450mm-2-14m2-pack</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
